--- a/templates/highlights/features.xlsx
+++ b/templates/highlights/features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sheetxl\workbook-templates\templates\highlights\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\sheetxl\templates-workbook\templates\highlights\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FF4FFB-186A-47F7-9240-52AF9394B8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B625E1-5EA1-40B2-86AD-4A47ADE708D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="756" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="1665" windowWidth="27420" windowHeight="12255" tabRatio="756" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feature Summary" sheetId="19" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1116" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="526">
   <si>
     <t>Multiple rows/columns</t>
   </si>
@@ -1464,9 +1464,6 @@
     <t>535+ Builtin Functions - 120,000+ Tests</t>
   </si>
   <si>
-    <t>375+ Excel compatible shortcut keys (all currently known)</t>
-  </si>
-  <si>
     <t>Excel Import/Export</t>
   </si>
   <si>
@@ -1627,6 +1624,9 @@
   </si>
   <si>
     <t>Autocorrect Formulas</t>
+  </si>
+  <si>
+    <t>450+ Excel compatible shortcut keys (all currently known)</t>
   </si>
 </sst>
 </file>
@@ -1860,10 +1860,10 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2326,7 +2326,7 @@
   <sheetPr codeName="Sheet16">
     <tabColor theme="7" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69.28515625" customWidth="1"/>
@@ -2353,22 +2353,22 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>471</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2388,262 +2388,267 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="16"/>
+        <v>116</v>
+      </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B12" s="16"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B12" s="16"/>
-    </row>
-    <row r="13" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="B13" s="16"/>
+    </row>
+    <row r="14" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>443</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>331</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>248</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>336</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>246</v>
+        <v>336</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>104</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>241</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B25" s="16"/>
+        <v>238</v>
+      </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>107</v>
+        <v>239</v>
       </c>
       <c r="B26" s="16"/>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="16"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B27" s="16"/>
-    </row>
-    <row r="28" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>464</v>
-      </c>
+      <c r="B28" s="16"/>
     </row>
     <row r="29" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B31" s="16" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="31" spans="1:2" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A31" s="36" t="s">
+    <row r="32" spans="1:2" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="A32" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="B31" s="36"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>232</v>
-      </c>
+      <c r="B32" s="36"/>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B35" s="7"/>
+        <v>245</v>
+      </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>337</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="B36" s="7"/>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>43</v>
+        <v>253</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B38" s="16"/>
+        <v>43</v>
+      </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>220</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="B39" s="16"/>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>364</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="43" spans="1:2" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A43" s="36" t="s">
+    <row r="44" spans="1:2" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="A44" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="B43" s="36"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B44" s="6"/>
+      <c r="B44" s="36"/>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="B45" s="6"/>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>235</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="B46" s="6"/>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="B47" s="6"/>
-    </row>
-    <row r="48" spans="1:2" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A48" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B48" s="6"/>
+    </row>
+    <row r="49" spans="1:2" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="A49" s="36" t="s">
         <v>242</v>
       </c>
-      <c r="B48" s="36"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>243</v>
-      </c>
+      <c r="B49" s="36"/>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>480</v>
+        <v>243</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B51" s="6"/>
-    </row>
-    <row r="52" spans="1:2" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.35">
-      <c r="A52" s="36" t="s">
+      <c r="B52" s="6"/>
+    </row>
+    <row r="53" spans="1:2" s="21" customFormat="1" ht="21" x14ac:dyDescent="0.35">
+      <c r="A53" s="36" t="s">
         <v>240</v>
       </c>
-      <c r="B52" s="36"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>14</v>
-      </c>
+      <c r="B53" s="36"/>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>346</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
         <v>323</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A44:B44"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3755,16 +3760,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A74:H74"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A65:H65"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A74:H74"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3996,7 +4001,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="21" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="35" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B1" s="35"/>
     </row>
@@ -4004,17 +4009,17 @@
       <c r="B2"/>
     </row>
     <row r="3" spans="1:2" s="21" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="B3" s="37"/>
+      <c r="B3" s="38"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>121</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4022,10 +4027,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -4033,7 +4038,7 @@
         <v>425</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -4041,7 +4046,7 @@
         <v>116</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -4049,7 +4054,7 @@
         <v>111</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4057,7 +4062,7 @@
         <v>375</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4065,7 +4070,7 @@
         <v>115</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4073,7 +4078,7 @@
         <v>113</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -4081,7 +4086,7 @@
         <v>106</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -4089,21 +4094,21 @@
         <v>228</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="B16" s="37"/>
+      <c r="B16" s="38"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>463</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4111,7 +4116,7 @@
         <v>466</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -4183,68 +4188,68 @@
   <sheetData>
     <row r="1" spans="1:1" s="21" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="34" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
@@ -4254,107 +4259,107 @@
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>35</v>
@@ -4362,7 +4367,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>35</v>
@@ -4370,7 +4375,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>35</v>
@@ -4382,55 +4387,55 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B41" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B42" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B43" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B45" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B46" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B47" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>222</v>
@@ -5851,16 +5856,16 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
@@ -5893,16 +5898,16 @@
       <c r="B6" s="6"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
@@ -6079,16 +6084,16 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="37" t="s">
         <v>247</v>
       </c>
-      <c r="B30" s="38"/>
-      <c r="C30" s="38"/>
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
@@ -6155,16 +6160,16 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="38" t="s">
+      <c r="A39" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="B39" s="38"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="38"/>
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="37"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
